--- a/database/event/2564/event_2564_evp_summary.xlsx
+++ b/database/event/2564/event_2564_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.2293</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0923</v>
+        <v>3.0212</v>
       </c>
       <c r="E2" t="n">
         <v>8.6976</v>
@@ -548,7 +548,7 @@
         <v>1.1236</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7901</v>
+        <v>2.7232</v>
       </c>
       <c r="E3" t="n">
         <v>7.9495</v>
@@ -594,7 +594,7 @@
         <v>1.0776</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6585</v>
+        <v>2.5935</v>
       </c>
       <c r="E4" t="n">
         <v>7.6239</v>
@@ -640,7 +640,7 @@
         <v>0.9171</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.1412</v>
       </c>
       <c r="E5" t="n">
         <v>6.4888</v>
@@ -686,7 +686,7 @@
         <v>0.9132</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1886</v>
+        <v>2.13</v>
       </c>
       <c r="E6" t="n">
         <v>6.4607</v>
@@ -732,7 +732,7 @@
         <v>0.9116</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1841</v>
+        <v>2.1256</v>
       </c>
       <c r="E7" t="n">
         <v>6.4496</v>
@@ -778,7 +778,7 @@
         <v>0.7904</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8376</v>
+        <v>1.7839</v>
       </c>
       <c r="E8" t="n">
         <v>5.5918</v>
@@ -824,7 +824,7 @@
         <v>0.7786</v>
       </c>
       <c r="D9" t="n">
-        <v>1.804</v>
+        <v>1.7507</v>
       </c>
       <c r="E9" t="n">
         <v>5.5086</v>
@@ -870,7 +870,7 @@
         <v>0.7776999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8014</v>
+        <v>1.7482</v>
       </c>
       <c r="E10" t="n">
         <v>5.5022</v>
@@ -916,7 +916,7 @@
         <v>0.7705</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7808</v>
+        <v>1.7279</v>
       </c>
       <c r="E11" t="n">
         <v>5.4513</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.3541</v>
+        <v>5.3396</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7568</v>
+        <v>0.7547</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7416</v>
+        <v>1.6834</v>
       </c>
       <c r="E12" t="n">
-        <v>5.3541</v>
+        <v>5.3396</v>
       </c>
       <c r="F12" t="n">
-        <v>5.3541</v>
+        <v>5.3396</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6.0921</v>
+        <v>6.0694</v>
       </c>
       <c r="I12" t="n">
         <v>6.1204</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.3007</v>
+        <v>5.2864</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7492</v>
+        <v>0.7472</v>
       </c>
       <c r="D13" t="n">
-        <v>1.72</v>
+        <v>1.6622</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3007</v>
+        <v>5.2864</v>
       </c>
       <c r="F13" t="n">
-        <v>5.3007</v>
+        <v>5.2864</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6.0084</v>
+        <v>5.986</v>
       </c>
       <c r="I13" t="n">
         <v>6.0364</v>
@@ -1054,7 +1054,7 @@
         <v>0.7471</v>
       </c>
       <c r="D14" t="n">
-        <v>1.714</v>
+        <v>1.662</v>
       </c>
       <c r="E14" t="n">
         <v>5.2858</v>
@@ -1100,7 +1100,7 @@
         <v>0.7251</v>
       </c>
       <c r="D15" t="n">
-        <v>1.651</v>
+        <v>1.5998</v>
       </c>
       <c r="E15" t="n">
         <v>5.1298</v>
@@ -1146,7 +1146,7 @@
         <v>0.7131</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6169</v>
+        <v>1.5662</v>
       </c>
       <c r="E16" t="n">
         <v>5.0455</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.041</v>
+        <v>5.0276</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7125</v>
+        <v>0.7106</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6151</v>
+        <v>1.5591</v>
       </c>
       <c r="E17" t="n">
-        <v>5.041</v>
+        <v>5.0276</v>
       </c>
       <c r="F17" t="n">
-        <v>5.041</v>
+        <v>5.0276</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.6011</v>
+        <v>5.5803</v>
       </c>
       <c r="I17" t="n">
         <v>5.6272</v>
@@ -1238,7 +1238,7 @@
         <v>0.6544</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4491</v>
+        <v>1.4007</v>
       </c>
       <c r="E18" t="n">
         <v>4.6301</v>
@@ -1284,7 +1284,7 @@
         <v>0.6363</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3973</v>
+        <v>1.3497</v>
       </c>
       <c r="E19" t="n">
         <v>4.502</v>
@@ -1330,7 +1330,7 @@
         <v>0.6314</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3833</v>
+        <v>1.3358</v>
       </c>
       <c r="E20" t="n">
         <v>4.4672</v>
@@ -1376,7 +1376,7 @@
         <v>0.6294</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3774</v>
+        <v>1.33</v>
       </c>
       <c r="E21" t="n">
         <v>4.4527</v>
@@ -1422,7 +1422,7 @@
         <v>0.6293</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3773</v>
+        <v>1.3299</v>
       </c>
       <c r="E22" t="n">
         <v>4.4524</v>
@@ -1468,7 +1468,7 @@
         <v>0.6217</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3555</v>
+        <v>1.3085</v>
       </c>
       <c r="E23" t="n">
         <v>4.3985</v>
@@ -1514,7 +1514,7 @@
         <v>0.6216</v>
       </c>
       <c r="D24" t="n">
-        <v>1.3553</v>
+        <v>1.3082</v>
       </c>
       <c r="E24" t="n">
         <v>4.3978</v>
@@ -1560,7 +1560,7 @@
         <v>0.6199</v>
       </c>
       <c r="D25" t="n">
-        <v>1.3503</v>
+        <v>1.3033</v>
       </c>
       <c r="E25" t="n">
         <v>4.3856</v>
@@ -1606,7 +1606,7 @@
         <v>0.6142</v>
       </c>
       <c r="D26" t="n">
-        <v>1.3342</v>
+        <v>1.2875</v>
       </c>
       <c r="E26" t="n">
         <v>4.3458</v>
@@ -1652,7 +1652,7 @@
         <v>0.6096</v>
       </c>
       <c r="D27" t="n">
-        <v>1.321</v>
+        <v>1.2744</v>
       </c>
       <c r="E27" t="n">
         <v>4.313</v>
@@ -1698,7 +1698,7 @@
         <v>0.6027</v>
       </c>
       <c r="D28" t="n">
-        <v>1.3012</v>
+        <v>1.2548</v>
       </c>
       <c r="E28" t="n">
         <v>4.2639</v>
@@ -1744,7 +1744,7 @@
         <v>0.5806</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2381</v>
+        <v>1.1926</v>
       </c>
       <c r="E29" t="n">
         <v>4.1077</v>
@@ -1790,7 +1790,7 @@
         <v>0.5790999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2337</v>
+        <v>1.1883</v>
       </c>
       <c r="E30" t="n">
         <v>4.0968</v>
@@ -1836,7 +1836,7 @@
         <v>0.5636</v>
       </c>
       <c r="D31" t="n">
-        <v>1.1895</v>
+        <v>1.1447</v>
       </c>
       <c r="E31" t="n">
         <v>3.9875</v>
@@ -1882,7 +1882,7 @@
         <v>0.5465</v>
       </c>
       <c r="D32" t="n">
-        <v>1.1405</v>
+        <v>1.0964</v>
       </c>
       <c r="E32" t="n">
         <v>3.8663</v>
@@ -1928,7 +1928,7 @@
         <v>0.5345</v>
       </c>
       <c r="D33" t="n">
-        <v>1.1063</v>
+        <v>1.0626</v>
       </c>
       <c r="E33" t="n">
         <v>3.7815</v>
@@ -1974,7 +1974,7 @@
         <v>0.5246</v>
       </c>
       <c r="D34" t="n">
-        <v>1.0782</v>
+        <v>1.0349</v>
       </c>
       <c r="E34" t="n">
         <v>3.7119</v>
@@ -2020,7 +2020,7 @@
         <v>0.5175</v>
       </c>
       <c r="D35" t="n">
-        <v>1.0578</v>
+        <v>1.0148</v>
       </c>
       <c r="E35" t="n">
         <v>3.6615</v>
@@ -2066,7 +2066,7 @@
         <v>0.5168</v>
       </c>
       <c r="D36" t="n">
-        <v>1.0559</v>
+        <v>1.0129</v>
       </c>
       <c r="E36" t="n">
         <v>3.6567</v>
@@ -2112,7 +2112,7 @@
         <v>0.5038</v>
       </c>
       <c r="D37" t="n">
-        <v>1.0185</v>
+        <v>0.9761</v>
       </c>
       <c r="E37" t="n">
         <v>3.5642</v>
@@ -2158,7 +2158,7 @@
         <v>0.4965</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9978</v>
+        <v>0.9556</v>
       </c>
       <c r="E38" t="n">
         <v>3.5129</v>
@@ -2204,7 +2204,7 @@
         <v>0.4776</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9438</v>
+        <v>0.9024</v>
       </c>
       <c r="E39" t="n">
         <v>3.3793</v>
@@ -2250,7 +2250,7 @@
         <v>0.4687</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9181</v>
+        <v>0.8771</v>
       </c>
       <c r="E40" t="n">
         <v>3.3158</v>
@@ -2296,7 +2296,7 @@
         <v>0.4674</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9146</v>
+        <v>0.8736</v>
       </c>
       <c r="E41" t="n">
         <v>3.3071</v>
@@ -2342,7 +2342,7 @@
         <v>0.4271</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7995</v>
+        <v>0.7601</v>
       </c>
       <c r="E42" t="n">
         <v>3.022</v>
@@ -2388,7 +2388,7 @@
         <v>0.4148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7643</v>
+        <v>0.7254</v>
       </c>
       <c r="E43" t="n">
         <v>2.935</v>
@@ -2434,7 +2434,7 @@
         <v>0.4139</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7228</v>
       </c>
       <c r="E44" t="n">
         <v>2.9284</v>
@@ -2480,7 +2480,7 @@
         <v>0.4107</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7526</v>
+        <v>0.7138</v>
       </c>
       <c r="E45" t="n">
         <v>2.9059</v>
@@ -2526,7 +2526,7 @@
         <v>0.3762</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="E46" t="n">
         <v>2.6613</v>
@@ -2572,7 +2572,7 @@
         <v>0.3722</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6424</v>
+        <v>0.6051</v>
       </c>
       <c r="E47" t="n">
         <v>2.6331</v>
@@ -2618,7 +2618,7 @@
         <v>0.3609</v>
       </c>
       <c r="D48" t="n">
-        <v>0.61</v>
+        <v>0.5732</v>
       </c>
       <c r="E48" t="n">
         <v>2.5531</v>
@@ -2664,7 +2664,7 @@
         <v>0.325</v>
       </c>
       <c r="D49" t="n">
-        <v>0.5077</v>
+        <v>0.4723</v>
       </c>
       <c r="E49" t="n">
         <v>2.2997</v>
@@ -2710,7 +2710,7 @@
         <v>0.3164</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4829</v>
+        <v>0.4478</v>
       </c>
       <c r="E50" t="n">
         <v>2.2383</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.1029</v>
+        <v>2.0951</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2972</v>
+        <v>0.2961</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4282</v>
+        <v>0.3908</v>
       </c>
       <c r="E51" t="n">
-        <v>2.1029</v>
+        <v>2.0951</v>
       </c>
       <c r="F51" t="n">
-        <v>2.1029</v>
+        <v>2.0951</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.1029</v>
+        <v>2.0951</v>
       </c>
       <c r="I51" t="n">
         <v>2.1127</v>
@@ -2802,7 +2802,7 @@
         <v>0.2841</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3907</v>
+        <v>0.357</v>
       </c>
       <c r="E52" t="n">
         <v>2.0102</v>
@@ -2848,7 +2848,7 @@
         <v>0.2733</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3598</v>
+        <v>0.3264</v>
       </c>
       <c r="E53" t="n">
         <v>1.9336</v>
@@ -2894,7 +2894,7 @@
         <v>0.2435</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2747</v>
+        <v>0.2425</v>
       </c>
       <c r="E54" t="n">
         <v>1.723</v>
@@ -2940,7 +2940,7 @@
         <v>0.2325</v>
       </c>
       <c r="D55" t="n">
-        <v>0.243</v>
+        <v>0.2113</v>
       </c>
       <c r="E55" t="n">
         <v>1.6446</v>
@@ -2986,7 +2986,7 @@
         <v>0.2143</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1912</v>
+        <v>0.1602</v>
       </c>
       <c r="E56" t="n">
         <v>1.5164</v>
@@ -3032,7 +3032,7 @@
         <v>0.2081</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1733</v>
+        <v>0.1426</v>
       </c>
       <c r="E57" t="n">
         <v>1.4721</v>
@@ -3078,7 +3078,7 @@
         <v>0.2019</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1556</v>
+        <v>0.1251</v>
       </c>
       <c r="E58" t="n">
         <v>1.4282</v>
@@ -3124,7 +3124,7 @@
         <v>0.1955</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1375</v>
+        <v>0.1072</v>
       </c>
       <c r="E59" t="n">
         <v>1.3833</v>
@@ -3170,7 +3170,7 @@
         <v>0.188</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1159</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E60" t="n">
         <v>1.33</v>
@@ -3216,7 +3216,7 @@
         <v>0.1852</v>
       </c>
       <c r="D61" t="n">
-        <v>0.108</v>
+        <v>0.0781</v>
       </c>
       <c r="E61" t="n">
         <v>1.3103</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.2686</v>
+        <v>1.2639</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1793</v>
+        <v>0.1786</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0911</v>
+        <v>0.0596</v>
       </c>
       <c r="E62" t="n">
-        <v>1.2686</v>
+        <v>1.2639</v>
       </c>
       <c r="F62" t="n">
-        <v>1.2686</v>
+        <v>1.2639</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.2686</v>
+        <v>1.2639</v>
       </c>
       <c r="I62" t="n">
         <v>1.2745</v>
@@ -3308,7 +3308,7 @@
         <v>0.1571</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0275</v>
+        <v>-0.0012</v>
       </c>
       <c r="E63" t="n">
         <v>1.1112</v>
@@ -3354,7 +3354,7 @@
         <v>0.1545</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0203</v>
+        <v>-0.0083</v>
       </c>
       <c r="E64" t="n">
         <v>1.0933</v>
@@ -3400,7 +3400,7 @@
         <v>0.1505</v>
       </c>
       <c r="D65" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0198</v>
       </c>
       <c r="E65" t="n">
         <v>1.0646</v>
@@ -3446,7 +3446,7 @@
         <v>0.1425</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.0141</v>
+        <v>-0.0423</v>
       </c>
       <c r="E66" t="n">
         <v>1.0081</v>
@@ -3492,7 +3492,7 @@
         <v>0.0993</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.1376</v>
+        <v>-0.1641</v>
       </c>
       <c r="E67" t="n">
         <v>0.7024</v>
@@ -3538,7 +3538,7 @@
         <v>0.0625</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.2426</v>
+        <v>-0.2676</v>
       </c>
       <c r="E68" t="n">
         <v>0.4425</v>
@@ -3584,7 +3584,7 @@
         <v>0.0252</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.3494</v>
+        <v>-0.3729</v>
       </c>
       <c r="E69" t="n">
         <v>0.1782</v>
@@ -3630,7 +3630,7 @@
         <v>0.0237</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.3537</v>
+        <v>-0.3771</v>
       </c>
       <c r="E70" t="n">
         <v>0.1676</v>
@@ -3676,7 +3676,7 @@
         <v>-0.0026</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.4288</v>
+        <v>-0.4512</v>
       </c>
       <c r="E71" t="n">
         <v>-0.0184</v>
@@ -3722,7 +3722,7 @@
         <v>-0.0121</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.4561</v>
+        <v>-0.4781</v>
       </c>
       <c r="E72" t="n">
         <v>-0.0859</v>
@@ -3768,7 +3768,7 @@
         <v>-0.0184</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.474</v>
+        <v>-0.4958</v>
       </c>
       <c r="E73" t="n">
         <v>-0.1302</v>
@@ -3814,7 +3814,7 @@
         <v>-0.0301</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.5074</v>
+        <v>-0.5288</v>
       </c>
       <c r="E74" t="n">
         <v>-0.2131</v>
@@ -3860,7 +3860,7 @@
         <v>-0.0331</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.5159</v>
+        <v>-0.5371</v>
       </c>
       <c r="E75" t="n">
         <v>-0.234</v>
@@ -3906,7 +3906,7 @@
         <v>-0.0386</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.5316</v>
+        <v>-0.5527</v>
       </c>
       <c r="E76" t="n">
         <v>-0.273</v>
@@ -3952,7 +3952,7 @@
         <v>-0.0576</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.5861</v>
+        <v>-0.6063</v>
       </c>
       <c r="E77" t="n">
         <v>-0.4077</v>
@@ -3998,7 +3998,7 @@
         <v>-0.0635</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.6029</v>
+        <v>-0.6229</v>
       </c>
       <c r="E78" t="n">
         <v>-0.4493</v>
@@ -4044,7 +4044,7 @@
         <v>-0.0771</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.6418</v>
+        <v>-0.6613</v>
       </c>
       <c r="E79" t="n">
         <v>-0.5456</v>
@@ -4090,7 +4090,7 @@
         <v>-0.0795</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.6681</v>
       </c>
       <c r="E80" t="n">
         <v>-0.5627</v>
@@ -4136,7 +4136,7 @@
         <v>-0.0852</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.6647999999999999</v>
+        <v>-0.6839</v>
       </c>
       <c r="E81" t="n">
         <v>-0.6025</v>
@@ -4182,7 +4182,7 @@
         <v>-0.089</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.6758</v>
+        <v>-0.6948</v>
       </c>
       <c r="E82" t="n">
         <v>-0.6298</v>
@@ -4228,7 +4228,7 @@
         <v>-0.0934</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.6883</v>
+        <v>-0.7071</v>
       </c>
       <c r="E83" t="n">
         <v>-0.6607</v>
@@ -4274,7 +4274,7 @@
         <v>-0.0946</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.6917</v>
+        <v>-0.7106</v>
       </c>
       <c r="E84" t="n">
         <v>-0.6693</v>
@@ -4320,7 +4320,7 @@
         <v>-0.1076</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.7289</v>
+        <v>-0.7472</v>
       </c>
       <c r="E85" t="n">
         <v>-0.7613</v>
@@ -4366,7 +4366,7 @@
         <v>-0.1146</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.7489</v>
+        <v>-0.7669</v>
       </c>
       <c r="E86" t="n">
         <v>-0.8108</v>
@@ -4412,7 +4412,7 @@
         <v>-0.1424</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.8284</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="E87" t="n">
         <v>-1.0075</v>
@@ -4458,7 +4458,7 @@
         <v>-0.1768</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.9268</v>
+        <v>-0.9423</v>
       </c>
       <c r="E88" t="n">
         <v>-1.2511</v>
@@ -4504,7 +4504,7 @@
         <v>-0.1772</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-0.9435</v>
       </c>
       <c r="E89" t="n">
         <v>-1.2539</v>
@@ -4550,7 +4550,7 @@
         <v>-0.1943</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.9768</v>
+        <v>-0.9917</v>
       </c>
       <c r="E90" t="n">
         <v>-1.375</v>
@@ -4596,7 +4596,7 @@
         <v>-0.2113</v>
       </c>
       <c r="D91" t="n">
-        <v>-1.0253</v>
+        <v>-1.0396</v>
       </c>
       <c r="E91" t="n">
         <v>-1.4951</v>
@@ -4642,7 +4642,7 @@
         <v>-0.2304</v>
       </c>
       <c r="D92" t="n">
-        <v>-1.08</v>
+        <v>-1.0935</v>
       </c>
       <c r="E92" t="n">
         <v>-1.6304</v>
@@ -4688,7 +4688,7 @@
         <v>-0.2479</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.1299</v>
+        <v>-1.1427</v>
       </c>
       <c r="E93" t="n">
         <v>-1.754</v>
@@ -4734,7 +4734,7 @@
         <v>-0.2567</v>
       </c>
       <c r="D94" t="n">
-        <v>-1.1551</v>
+        <v>-1.1675</v>
       </c>
       <c r="E94" t="n">
         <v>-1.8163</v>
@@ -4780,7 +4780,7 @@
         <v>-0.2819</v>
       </c>
       <c r="D95" t="n">
-        <v>-1.227</v>
+        <v>-1.2384</v>
       </c>
       <c r="E95" t="n">
         <v>-1.9943</v>
@@ -4826,7 +4826,7 @@
         <v>-0.2852</v>
       </c>
       <c r="D96" t="n">
-        <v>-1.2364</v>
+        <v>-1.2477</v>
       </c>
       <c r="E96" t="n">
         <v>-2.0176</v>
@@ -4872,7 +4872,7 @@
         <v>-0.3028</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.2869</v>
+        <v>-1.2975</v>
       </c>
       <c r="E97" t="n">
         <v>-2.1425</v>
@@ -4918,7 +4918,7 @@
         <v>-0.309</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.3047</v>
+        <v>-1.315</v>
       </c>
       <c r="E98" t="n">
         <v>-2.1865</v>
@@ -4964,7 +4964,7 @@
         <v>-0.3266</v>
       </c>
       <c r="D99" t="n">
-        <v>-1.3547</v>
+        <v>-1.3644</v>
       </c>
       <c r="E99" t="n">
         <v>-2.3104</v>
@@ -5010,7 +5010,7 @@
         <v>-0.3368</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.384</v>
+        <v>-1.3932</v>
       </c>
       <c r="E100" t="n">
         <v>-2.3828</v>
@@ -5056,7 +5056,7 @@
         <v>-0.3407</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.3952</v>
+        <v>-1.4043</v>
       </c>
       <c r="E101" t="n">
         <v>-2.4106</v>
@@ -5102,7 +5102,7 @@
         <v>-0.3433</v>
       </c>
       <c r="D102" t="n">
-        <v>-1.4026</v>
+        <v>-1.4116</v>
       </c>
       <c r="E102" t="n">
         <v>-2.4289</v>
@@ -5148,7 +5148,7 @@
         <v>-0.3455</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.4089</v>
+        <v>-1.4178</v>
       </c>
       <c r="E103" t="n">
         <v>-2.4446</v>
@@ -5194,7 +5194,7 @@
         <v>-0.3651</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.4649</v>
+        <v>-1.473</v>
       </c>
       <c r="E104" t="n">
         <v>-2.5831</v>
@@ -5240,7 +5240,7 @@
         <v>-0.3682</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.4738</v>
+        <v>-1.4819</v>
       </c>
       <c r="E105" t="n">
         <v>-2.6053</v>
@@ -5286,7 +5286,7 @@
         <v>-0.3768</v>
       </c>
       <c r="D106" t="n">
-        <v>-1.4984</v>
+        <v>-1.5061</v>
       </c>
       <c r="E106" t="n">
         <v>-2.6662</v>
@@ -5332,7 +5332,7 @@
         <v>-0.385</v>
       </c>
       <c r="D107" t="n">
-        <v>-1.5218</v>
+        <v>-1.5292</v>
       </c>
       <c r="E107" t="n">
         <v>-2.724</v>
@@ -5378,7 +5378,7 @@
         <v>-0.4214</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.6257</v>
+        <v>-1.6316</v>
       </c>
       <c r="E108" t="n">
         <v>-2.9812</v>
@@ -5424,7 +5424,7 @@
         <v>-0.4501</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.7077</v>
+        <v>-1.7125</v>
       </c>
       <c r="E109" t="n">
         <v>-3.1842</v>
@@ -5470,7 +5470,7 @@
         <v>-0.4565</v>
       </c>
       <c r="D110" t="n">
-        <v>-1.7262</v>
+        <v>-1.7307</v>
       </c>
       <c r="E110" t="n">
         <v>-3.2299</v>
@@ -5516,7 +5516,7 @@
         <v>-0.4745</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.7776</v>
+        <v>-1.7814</v>
       </c>
       <c r="E111" t="n">
         <v>-3.3571</v>
@@ -5562,7 +5562,7 @@
         <v>-0.6095</v>
       </c>
       <c r="D112" t="n">
-        <v>-2.1634</v>
+        <v>-2.1619</v>
       </c>
       <c r="E112" t="n">
         <v>-4.3123</v>
@@ -5608,7 +5608,7 @@
         <v>-0.6096</v>
       </c>
       <c r="D113" t="n">
-        <v>-2.1638</v>
+        <v>-2.1623</v>
       </c>
       <c r="E113" t="n">
         <v>-4.3132</v>
@@ -5654,7 +5654,7 @@
         <v>-0.612</v>
       </c>
       <c r="D114" t="n">
-        <v>-2.1705</v>
+        <v>-2.1689</v>
       </c>
       <c r="E114" t="n">
         <v>-4.3298</v>
@@ -5700,7 +5700,7 @@
         <v>-0.6341</v>
       </c>
       <c r="D115" t="n">
-        <v>-2.2337</v>
+        <v>-2.2312</v>
       </c>
       <c r="E115" t="n">
         <v>-4.4862</v>
@@ -5746,7 +5746,7 @@
         <v>-0.6863</v>
       </c>
       <c r="D116" t="n">
-        <v>-2.383</v>
+        <v>-2.3785</v>
       </c>
       <c r="E116" t="n">
         <v>-4.8558</v>
